--- a/sample-data/answer-keys/Complex_Test_Answer_Key_FY2025.xlsx
+++ b/sample-data/answer-keys/Complex_Test_Answer_Key_FY2025.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="11_6F480E75D92F8BFC2A8458B55494918721F804C4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
